--- a/AAII_Financials/Yearly/TURB_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TURB_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="92">
   <si>
     <t>TURB</t>
   </si>
@@ -715,7 +715,7 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>23500</v>
+        <v>23300</v>
       </c>
       <c r="E8" s="3">
         <v>9700</v>
@@ -781,7 +781,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>4600</v>
+        <v>4400</v>
       </c>
       <c r="E10" s="3">
         <v>300</v>
@@ -973,7 +973,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>24300</v>
+        <v>24200</v>
       </c>
       <c r="E17" s="3">
         <v>13900</v>
@@ -1683,7 +1683,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="E42" s="3">
         <v>200</v>
@@ -1716,7 +1716,7 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>14300</v>
+        <v>14000</v>
       </c>
       <c r="E43" s="3">
         <v>3200</v>
@@ -1749,7 +1749,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4000</v>
+        <v>8000</v>
       </c>
       <c r="E44" s="3">
         <v>2800</v>
@@ -1781,8 +1781,8 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>0</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>14800</v>
+        <v>14400</v>
       </c>
       <c r="E57" s="3">
         <v>2200</v>
@@ -2175,7 +2175,7 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>5600</v>
+        <v>6800</v>
       </c>
       <c r="E58" s="3">
         <v>6600</v>
@@ -2208,7 +2208,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3400</v>
+        <v>2500</v>
       </c>
       <c r="E59" s="3">
         <v>600</v>
@@ -2619,7 +2619,7 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-7600</v>
+        <v>-6000</v>
       </c>
       <c r="E72" s="3">
         <v>-4100</v>
